--- a/Raw_Data/Resperation/Spats/TotalSpatsOxy.xlsx
+++ b/Raw_Data/Resperation/Spats/TotalSpatsOxy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\Stylophora pistillata\Physiology\Resperation\Full tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\Stylophora-pistillata-FPs\Raw_Data\Resperation\Spats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378E8EDA-C346-4929-A8C7-8D6B2C76712F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BFEE94-6309-41F2-97AC-9AB654E91B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{F0BF1E01-85D4-43B6-A295-C4ABE3B0DADF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F0BF1E01-85D4-43B6-A295-C4ABE3B0DADF}"/>
   </bookViews>
   <sheets>
     <sheet name="TotalSpatsOxy" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5198" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5198" uniqueCount="290">
   <si>
     <t>date</t>
   </si>
@@ -911,6 +911,9 @@
   </si>
   <si>
     <t>plateA_HF_7.8_1</t>
+  </si>
+  <si>
+    <t>morph</t>
   </si>
 </sst>
 </file>
@@ -1809,7 +1812,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>289</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>

--- a/Raw_Data/Resperation/Spats/TotalSpatsOxy.xlsx
+++ b/Raw_Data/Resperation/Spats/TotalSpatsOxy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\Stylophora-pistillata-FPs\Raw_Data\Resperation\Spats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BFEE94-6309-41F2-97AC-9AB654E91B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D271A888-19A0-4D6A-A882-93998EFB3AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F0BF1E01-85D4-43B6-A295-C4ABE3B0DADF}"/>
   </bookViews>
@@ -1457,7 +1457,18 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1787,7 +1798,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10758E95-B21C-4274-9E23-53FE35BC8D40}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1827,7 +1837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45791</v>
       </c>
@@ -1856,7 +1866,7 @@
         <v>2.5520041543291163</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45791</v>
       </c>
@@ -1885,7 +1895,7 @@
         <v>2.1534538875950422</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45791</v>
       </c>
@@ -1914,7 +1924,7 @@
         <v>2.1498150123554631</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45791</v>
       </c>
@@ -1943,7 +1953,7 @@
         <v>2.0620812146762604</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45791</v>
       </c>
@@ -1972,7 +1982,7 @@
         <v>2.0416033234632902</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45791</v>
       </c>
@@ -2001,7 +2011,7 @@
         <v>1.987697959199924</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45791</v>
       </c>
@@ -2030,7 +2040,7 @@
         <v>1.9742015068526981</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45791</v>
       </c>
@@ -2059,7 +2069,7 @@
         <v>1.9178459259177847</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45791</v>
       </c>
@@ -2088,7 +2098,7 @@
         <v>1.7475823168167748</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45791</v>
       </c>
@@ -2117,7 +2127,7 @@
         <v>1.7227631100760299</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45791</v>
       </c>
@@ -2146,7 +2156,7 @@
         <v>1.7198520098843699</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45791</v>
       </c>
@@ -2175,7 +2185,7 @@
         <v>1.6496649717409999</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45791</v>
       </c>
@@ -2204,7 +2214,7 @@
         <v>1.6083903554208672</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45791</v>
       </c>
@@ -2233,7 +2243,7 @@
         <v>1.6075856167201255</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45791</v>
       </c>
@@ -2262,7 +2272,7 @@
         <v>1.59015836735993</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45791</v>
       </c>
@@ -2291,7 +2301,7 @@
         <v>1.5342767407342199</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45791</v>
       </c>
@@ -2320,7 +2330,7 @@
         <v>1.4311848685779105</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45791</v>
       </c>
@@ -2349,7 +2359,7 @@
         <v>1.3980658534534101</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45791</v>
       </c>
@@ -2378,7 +2388,7 @@
         <v>1.316164543636112</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45791</v>
       </c>
@@ -2407,7 +2417,7 @@
         <v>1.28671228433669</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45791</v>
       </c>
@@ -2436,7 +2446,7 @@
         <v>1.2860684933761</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>45791</v>
       </c>
@@ -2465,7 +2475,7 @@
         <v>1.2609299651346402</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45791</v>
       </c>
@@ -2494,7 +2504,7 @@
         <v>1.221805031475673</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>45791</v>
       </c>
@@ -2523,7 +2533,7 @@
         <v>1.1904621509087028</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45791</v>
       </c>
@@ -2552,7 +2562,7 @@
         <v>1.14494789486232</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>45791</v>
       </c>
@@ -2581,7 +2591,7 @@
         <v>1.0949213180804085</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45791</v>
       </c>
@@ -2610,7 +2620,7 @@
         <v>1.0087439721077101</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45791</v>
       </c>
@@ -2639,7 +2649,7 @@
         <v>0.97744402518053797</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45791</v>
       </c>
@@ -2668,7 +2678,7 @@
         <v>0.95236972072696202</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>45791</v>
       </c>
@@ -2697,7 +2707,7 @@
         <v>0.87593705446432601</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45791</v>
       </c>
@@ -2726,7 +2736,7 @@
         <v>0.81906590770514787</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>45791</v>
       </c>
@@ -2755,7 +2765,7 @@
         <v>0.80042576474540927</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45791</v>
       </c>
@@ -2784,7 +2794,7 @@
         <v>0.7291750444125582</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>45791</v>
       </c>
@@ -2813,7 +2823,7 @@
         <v>0.69483317543831269</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45791</v>
       </c>
@@ -2842,7 +2852,7 @@
         <v>0.655252726164118</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45791</v>
       </c>
@@ -2871,7 +2881,7 @@
         <v>0.6341196884078486</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45791</v>
       </c>
@@ -2900,7 +2910,7 @@
         <v>0.58334003553004599</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>45791</v>
       </c>
@@ -2929,7 +2939,7 @@
         <v>0.55586654035064997</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>45791</v>
       </c>
@@ -2958,7 +2968,7 @@
         <v>0.50729575072627797</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>45791</v>
       </c>
@@ -2987,7 +2997,7 @@
         <v>2.3599474135470615</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45791</v>
       </c>
@@ -3016,7 +3026,7 @@
         <v>2.0376889647763781</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>45791</v>
       </c>
@@ -3045,7 +3055,7 @@
         <v>1.6301511718210999</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45791</v>
       </c>
@@ -3074,7 +3084,7 @@
         <v>1.6184006481555111</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45791</v>
       </c>
@@ -3103,7 +3113,7 @@
         <v>1.3379679484218725</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45791</v>
       </c>
@@ -3132,7 +3142,7 @@
         <v>1.2947205185244</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45791</v>
       </c>
@@ -3161,7 +3171,7 @@
         <v>1.2940949761579212</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>45791</v>
       </c>
@@ -3190,7 +3200,7 @@
         <v>1.2388790406575159</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>45791</v>
       </c>
@@ -3219,7 +3229,7 @@
         <v>1.2367481754424181</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45791</v>
       </c>
@@ -3248,7 +3258,7 @@
         <v>1.0798717386136358</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>45791</v>
       </c>
@@ -3277,7 +3287,7 @@
         <v>1.0759785598074403</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>45791</v>
       </c>
@@ -3306,7 +3316,7 @@
         <v>1.0703743587374901</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>45791</v>
       </c>
@@ -3335,7 +3345,7 @@
         <v>1.0352759809263301</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>45791</v>
       </c>
@@ -3364,7 +3374,7 @@
         <v>0.99110323252601196</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45791</v>
       </c>
@@ -3393,7 +3403,7 @@
         <v>0.98939854035393404</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>45791</v>
       </c>
@@ -3422,7 +3432,7 @@
         <v>0.91415482192188802</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>45791</v>
       </c>
@@ -3451,7 +3461,7 @@
         <v>0.87921265884429589</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>45791</v>
       </c>
@@ -3480,7 +3490,7 @@
         <v>0.863897390890908</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>45791</v>
       </c>
@@ -3509,7 +3519,7 @@
         <v>0.86078284784595205</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>45791</v>
       </c>
@@ -3538,7 +3548,7 @@
         <v>0.77250438243554276</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>45791</v>
       </c>
@@ -3567,7 +3577,7 @@
         <v>0.74425525767018974</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45791</v>
       </c>
@@ -3596,7 +3606,7 @@
         <v>0.73132385753750995</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>45791</v>
       </c>
@@ -3625,7 +3635,7 @@
         <v>0.703370127075436</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>45791</v>
       </c>
@@ -3654,7 +3664,7 @@
         <v>0.67755693547971629</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>45791</v>
       </c>
@@ -3683,7 +3693,7 @@
         <v>0.64719583268020908</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>45791</v>
       </c>
@@ -3712,7 +3722,7 @@
         <v>0.61800350594843401</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>45791</v>
       </c>
@@ -3741,7 +3751,7 @@
         <v>0.60466286203930619</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>45791</v>
       </c>
@@ -3770,7 +3780,7 @@
         <v>0.59540420613615097</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>45791</v>
       </c>
@@ -3799,7 +3809,7 @@
         <v>0.54204554838377295</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>45791</v>
       </c>
@@ -3828,7 +3838,7 @@
         <v>0.53746647605108777</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>45791</v>
       </c>
@@ -3857,7 +3867,7 @@
         <v>0.51775666614416704</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>45791</v>
       </c>
@@ -3886,7 +3896,7 @@
         <v>0.49031229884440236</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>45791</v>
       </c>
@@ -3915,7 +3925,7 @@
         <v>0.48373028963144499</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>45791</v>
       </c>
@@ -3944,7 +3954,7 @@
         <v>0.42997318084087</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>45791</v>
       </c>
@@ -3973,7 +3983,7 @@
         <v>0.39224983907552102</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>45791</v>
       </c>
@@ -4002,7 +4012,7 @@
         <v>0.3150139865572496</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>45791</v>
       </c>
@@ -4031,7 +4041,7 @@
         <v>0.30747088162040365</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>45791</v>
       </c>
@@ -4060,7 +4070,7 @@
         <v>0.28229914453848509</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>45791</v>
       </c>
@@ -4089,7 +4099,7 @@
         <v>0.25201118924579902</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>45791</v>
       </c>
@@ -4118,7 +4128,7 @@
         <v>0.24597670529632201</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>45791</v>
       </c>
@@ -4147,7 +4157,7 @@
         <v>0.22583931563078799</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>45791</v>
       </c>
@@ -4176,7 +4186,7 @@
         <v>0.20000637055420964</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>45791</v>
       </c>
@@ -4205,7 +4215,7 @@
         <v>0.160005096443367</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>45791</v>
       </c>
@@ -4234,7 +4244,7 @@
         <v>2.7493383387180183E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>45791</v>
       </c>
@@ -5553,7 +5563,7 @@
         <v>1.971122222</v>
       </c>
       <c r="E130" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F130">
         <v>23</v>
@@ -5582,7 +5592,7 @@
         <v>2.04798151699999</v>
       </c>
       <c r="E131" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F131">
         <v>23</v>
@@ -5843,7 +5853,7 @@
         <v>1.684232639</v>
       </c>
       <c r="E140" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F140">
         <v>23</v>
@@ -5872,7 +5882,7 @@
         <v>1.97127651499999</v>
       </c>
       <c r="E141" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F141">
         <v>23</v>
@@ -6481,7 +6491,7 @@
         <v>1.60319146699999</v>
       </c>
       <c r="E162" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F162">
         <v>23</v>
@@ -6510,7 +6520,7 @@
         <v>6.0211309210000001</v>
       </c>
       <c r="E163" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F163">
         <v>23</v>
@@ -6568,7 +6578,7 @@
         <v>1.6230633670000001</v>
       </c>
       <c r="E165" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F165">
         <v>23</v>
@@ -6684,7 +6694,7 @@
         <v>2.1616264389999902</v>
       </c>
       <c r="E169" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F169">
         <v>23</v>
@@ -6713,7 +6723,7 @@
         <v>2.2045252679999998</v>
       </c>
       <c r="E170" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F170">
         <v>23</v>
@@ -6829,7 +6839,7 @@
         <v>3.690246406</v>
       </c>
       <c r="E174" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F174">
         <v>23</v>
@@ -6887,7 +6897,7 @@
         <v>1.621366141</v>
       </c>
       <c r="E176" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F176">
         <v>23</v>
@@ -7090,7 +7100,7 @@
         <v>1.8328701649999899</v>
       </c>
       <c r="E183" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F183">
         <v>23</v>
@@ -7119,7 +7129,7 @@
         <v>1.890415398</v>
       </c>
       <c r="E184" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F184">
         <v>23</v>
@@ -7206,7 +7216,7 @@
         <v>0.68100000000000005</v>
       </c>
       <c r="E187" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F187">
         <v>23</v>
@@ -7960,7 +7970,7 @@
         <v>3.5821507189999999</v>
       </c>
       <c r="E213" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F213">
         <v>23</v>
@@ -8047,7 +8057,7 @@
         <v>1.6230633670000001</v>
       </c>
       <c r="E216" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F216">
         <v>23</v>
@@ -8221,7 +8231,7 @@
         <v>1.97127651499999</v>
       </c>
       <c r="E222" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F222">
         <v>23</v>
@@ -8250,7 +8260,7 @@
         <v>2.5139868339999998</v>
       </c>
       <c r="E223" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F223">
         <v>23</v>
@@ -8366,7 +8376,7 @@
         <v>1.291518476</v>
       </c>
       <c r="E227" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F227">
         <v>23</v>
@@ -8395,7 +8405,7 @@
         <v>2.2045252679999998</v>
       </c>
       <c r="E228" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F228">
         <v>23</v>
@@ -8482,7 +8492,7 @@
         <v>2.35078458</v>
       </c>
       <c r="E231" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F231">
         <v>23</v>
@@ -8946,7 +8956,7 @@
         <v>2.1894258169999898</v>
       </c>
       <c r="E247" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F247">
         <v>23</v>
@@ -8975,7 +8985,7 @@
         <v>2.35078458</v>
       </c>
       <c r="E248" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F248">
         <v>23</v>
@@ -9222,7 +9232,7 @@
         <v>1.06077041795788E-4</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>45791</v>
       </c>
@@ -9280,7 +9290,7 @@
         <v>1.0561805868084799</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>45791</v>
       </c>
@@ -9309,7 +9319,7 @@
         <v>1.57936120548215</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>45791</v>
       </c>
@@ -9338,7 +9348,7 @@
         <v>1.05293163490888</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>45791</v>
       </c>
@@ -9367,7 +9377,7 @@
         <v>0.64034061179632695</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>45389</v>
       </c>
@@ -9396,7 +9406,7 @@
         <v>1.5347369423869299</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>45389</v>
       </c>
@@ -9425,7 +9435,7 @@
         <v>1.48600376008221</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>45389</v>
       </c>
@@ -9454,7 +9464,7 @@
         <v>1.37691951047203</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>45755</v>
       </c>
@@ -9483,7 +9493,7 @@
         <v>1.19122256490099</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>45755</v>
       </c>
@@ -9497,7 +9507,7 @@
         <v>1.1912765089999999</v>
       </c>
       <c r="E266" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F266">
         <v>23</v>
@@ -9512,7 +9522,7 @@
         <v>1.09342171510515</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>45389</v>
       </c>
@@ -9541,7 +9551,7 @@
         <v>1.0764395428129401</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>45755</v>
       </c>
@@ -9555,7 +9565,7 @@
         <v>1.72012442999999</v>
       </c>
       <c r="E268" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F268">
         <v>23</v>
@@ -9570,7 +9580,7 @@
         <v>1.00076916830691</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>45389</v>
       </c>
@@ -9599,7 +9609,7 @@
         <v>0.99138257706230104</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>45389</v>
       </c>
@@ -9628,7 +9638,7 @@
         <v>0.98281668042912995</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>45389</v>
       </c>
@@ -9657,7 +9667,7 @@
         <v>0.80896102677542603</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>45755</v>
       </c>
@@ -9671,7 +9681,7 @@
         <v>3.2728172400000002</v>
       </c>
       <c r="E272" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F272">
         <v>23</v>
@@ -9686,7 +9696,7 @@
         <v>0.80533941723667402</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>45755</v>
       </c>
@@ -9700,7 +9710,7 @@
         <v>5.51087955399999</v>
       </c>
       <c r="E273" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F273">
         <v>23</v>
@@ -9715,7 +9725,7 @@
         <v>0.76600476976833598</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>45389</v>
       </c>
@@ -9744,7 +9754,7 @@
         <v>0.73467956236696197</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>45389</v>
       </c>
@@ -9773,7 +9783,7 @@
         <v>0.60379035588630303</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>45755</v>
       </c>
@@ -9787,7 +9797,7 @@
         <v>2.1942331880000001</v>
       </c>
       <c r="E276" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F276">
         <v>23</v>
@@ -9802,7 +9812,7 @@
         <v>0.58356434251247202</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>45389</v>
       </c>
@@ -9831,7 +9841,7 @@
         <v>0.55364944754017298</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>45755</v>
       </c>
@@ -9845,7 +9855,7 @@
         <v>3.1225432009999898</v>
       </c>
       <c r="E278" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F278">
         <v>23</v>
@@ -9860,7 +9870,7 @@
         <v>0.52303381124140502</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>45755</v>
       </c>
@@ -9889,7 +9899,7 @@
         <v>0.48857162247000402</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>45755</v>
       </c>
@@ -9918,7 +9928,7 @@
         <v>0.46128560609847702</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>45389</v>
       </c>
@@ -9947,7 +9957,7 @@
         <v>0.40972753203592499</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>45755</v>
       </c>
@@ -9961,7 +9971,7 @@
         <v>11.06119524</v>
       </c>
       <c r="E282" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F282">
         <v>23</v>
@@ -9976,7 +9986,7 @@
         <v>0.38194769801612599</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>45389</v>
       </c>
@@ -10005,7 +10015,7 @@
         <v>0.249733186190947</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>45755</v>
       </c>
@@ -10034,7 +10044,7 @@
         <v>0.240115658846484</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>45755</v>
       </c>
@@ -10048,7 +10058,7 @@
         <v>9.3673361899999996</v>
       </c>
       <c r="E285" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F285">
         <v>23</v>
@@ -10063,7 +10073,7 @@
         <v>0.214865424578493</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>45755</v>
       </c>
@@ -10077,7 +10087,7 @@
         <v>4.0028284659999898</v>
       </c>
       <c r="E286" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F286">
         <v>23</v>
@@ -10092,7 +10102,7 @@
         <v>0.20837432306081599</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>45755</v>
       </c>
@@ -10121,7 +10131,7 @@
         <v>0.20675306797144399</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>45755</v>
       </c>
@@ -10135,7 +10145,7 @@
         <v>2.4035149759999999</v>
       </c>
       <c r="E288" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F288">
         <v>23</v>
@@ -10150,7 +10160,7 @@
         <v>0.148461859632118</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>45755</v>
       </c>
@@ -10179,7 +10189,7 @@
         <v>5.8761168469259099E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>45389</v>
       </c>
@@ -10208,7 +10218,7 @@
         <v>5.02429894246866E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>45389</v>
       </c>
@@ -10237,7 +10247,7 @@
         <v>3.8657321048020603E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>45389</v>
       </c>
@@ -10266,7 +10276,7 @@
         <v>3.18014239228675E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>45755</v>
       </c>
@@ -10280,7 +10290,7 @@
         <v>1.68357822299999</v>
       </c>
       <c r="E293" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F293">
         <v>23</v>
@@ -10295,7 +10305,7 @@
         <v>1.36740828634611E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>45755</v>
       </c>
@@ -10309,7 +10319,7 @@
         <v>8.4945216319999997</v>
       </c>
       <c r="E294" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F294">
         <v>23</v>
@@ -10324,7 +10334,7 @@
         <v>1.32505616533731E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>45389</v>
       </c>
@@ -10353,7 +10363,7 @@
         <v>1.1828452987957301E-2</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>45755</v>
       </c>
@@ -10367,7 +10377,7 @@
         <v>5.1987121449999902</v>
       </c>
       <c r="E296" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F296">
         <v>23</v>
@@ -10382,7 +10392,7 @@
         <v>4.5568978843915798E-3</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>45755</v>
       </c>
@@ -10396,7 +10406,7 @@
         <v>2.011446968</v>
       </c>
       <c r="E297" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F297">
         <v>23</v>
@@ -10411,7 +10421,7 @@
         <v>2.7460745818240601E-3</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>45389</v>
       </c>
@@ -10440,7 +10450,7 @@
         <v>3.10794250018097</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>45389</v>
       </c>
@@ -10469,7 +10479,7 @@
         <v>1.0580951471889699</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>45755</v>
       </c>
@@ -10498,7 +10508,7 @@
         <v>1.0377926770439401</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>45755</v>
       </c>
@@ -10527,7 +10537,7 @@
         <v>0.95594055837414205</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>45389</v>
       </c>
@@ -10556,7 +10566,7 @@
         <v>0.84876041596807195</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>45755</v>
       </c>
@@ -10585,7 +10595,7 @@
         <v>0.80910028431290504</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>45755</v>
       </c>
@@ -10614,7 +10624,7 @@
         <v>0.67899000964178802</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>45389</v>
       </c>
@@ -10643,7 +10653,7 @@
         <v>0.66352358554836499</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>45389</v>
       </c>
@@ -10672,7 +10682,7 @@
         <v>0.62910598647805305</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>45755</v>
       </c>
@@ -10686,7 +10696,7 @@
         <v>2.0217623140000001</v>
       </c>
       <c r="E307" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F307">
         <v>23</v>
@@ -10701,7 +10711,7 @@
         <v>0.61600265666169196</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>45389</v>
       </c>
@@ -10730,7 +10740,7 @@
         <v>0.59999647589239602</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>45755</v>
       </c>
@@ -10744,7 +10754,7 @@
         <v>1.8503585309999999</v>
       </c>
       <c r="E309" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F309">
         <v>23</v>
@@ -10759,7 +10769,7 @@
         <v>0.55501524861792595</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>45755</v>
       </c>
@@ -10773,7 +10783,7 @@
         <v>6.5452771219999999</v>
       </c>
       <c r="E310" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F310">
         <v>23</v>
@@ -10788,7 +10798,7 @@
         <v>0.39802303342113998</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>45389</v>
       </c>
@@ -10817,7 +10827,7 @@
         <v>0.37714164778006598</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>45755</v>
       </c>
@@ -10831,7 +10841,7 @@
         <v>3.175212916</v>
       </c>
       <c r="E312" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F312">
         <v>23</v>
@@ -10846,7 +10856,7 @@
         <v>0.34198898292418001</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>45755</v>
       </c>
@@ -10875,7 +10885,7 @@
         <v>0.31551438011336402</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>45755</v>
       </c>
@@ -10904,7 +10914,7 @@
         <v>0.305664035542974</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>45755</v>
       </c>
@@ -10933,7 +10943,7 @@
         <v>0.24584206562290101</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>45755</v>
       </c>
@@ -10962,7 +10972,7 @@
         <v>0.21788134143690399</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>45755</v>
       </c>
@@ -10991,7 +11001,7 @@
         <v>0.168250629976957</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>45389</v>
       </c>
@@ -11020,7 +11030,7 @@
         <v>8.7737640081694601E-2</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>45755</v>
       </c>
@@ -11034,7 +11044,7 @@
         <v>2.2757605970000001</v>
       </c>
       <c r="E319" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F319">
         <v>23</v>
@@ -11049,7 +11059,7 @@
         <v>8.2565641204959198E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>45755</v>
       </c>
@@ -11063,7 +11073,7 @@
         <v>3.422052903</v>
       </c>
       <c r="E320" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F320">
         <v>23</v>
@@ -11078,7 +11088,7 @@
         <v>7.0780756006921797E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>45389</v>
       </c>
@@ -11107,7 +11117,7 @@
         <v>1.7858780158597799E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>45755</v>
       </c>
@@ -11136,7 +11146,7 @@
         <v>0.68925853910269297</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>45454</v>
       </c>
@@ -11165,7 +11175,7 @@
         <v>0.66658678619607503</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>45390</v>
       </c>
@@ -11179,7 +11189,7 @@
         <v>4.0028284659999898</v>
       </c>
       <c r="E324" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F324">
         <v>27</v>
@@ -11194,7 +11204,7 @@
         <v>0.55140683128215395</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>45454</v>
       </c>
@@ -11223,7 +11233,7 @@
         <v>0.54569765025539196</v>
       </c>
     </row>
-    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>45454</v>
       </c>
@@ -11252,7 +11262,7 @@
         <v>0.54068367473608903</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>45755</v>
       </c>
@@ -11281,7 +11291,7 @@
         <v>0.53534135355807499</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>45755</v>
       </c>
@@ -11310,7 +11320,7 @@
         <v>0.51282191844252301</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>45454</v>
       </c>
@@ -11339,7 +11349,7 @@
         <v>0.49782981478337701</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>45755</v>
       </c>
@@ -11368,7 +11378,7 @@
         <v>0.49279782151221502</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>45755</v>
       </c>
@@ -11397,7 +11407,7 @@
         <v>0.48839996962012699</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>45454</v>
       </c>
@@ -11426,7 +11436,7 @@
         <v>0.46940384018947701</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>45454</v>
       </c>
@@ -11455,7 +11465,7 @@
         <v>0.45887085031866698</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>45755</v>
       </c>
@@ -11484,7 +11494,7 @@
         <v>0.43023741252975201</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>45390</v>
       </c>
@@ -11513,7 +11523,7 @@
         <v>0.42827308284645998</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>45454</v>
       </c>
@@ -11542,7 +11552,7 @@
         <v>0.41434826877636599</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>45390</v>
       </c>
@@ -11556,7 +11566,7 @@
         <v>8.4945216319999997</v>
       </c>
       <c r="E337" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F337">
         <v>27</v>
@@ -11571,7 +11581,7 @@
         <v>0.41025753475401799</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>45390</v>
       </c>
@@ -11600,7 +11610,7 @@
         <v>0.39071997569610201</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>45454</v>
       </c>
@@ -11629,7 +11639,7 @@
         <v>0.38947213585014501</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>45755</v>
       </c>
@@ -11658,7 +11668,7 @@
         <v>0.38820748022445201</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>45755</v>
       </c>
@@ -11687,7 +11697,7 @@
         <v>0.30748544643798498</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>45755</v>
       </c>
@@ -11716,7 +11726,7 @@
         <v>0.29936075307596999</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>45755</v>
       </c>
@@ -11745,7 +11755,7 @@
         <v>0.273462663090633</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>45755</v>
       </c>
@@ -11774,7 +11784,7 @@
         <v>0.25597665323006003</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>45755</v>
       </c>
@@ -11803,7 +11813,7 @@
         <v>0.25173819461837199</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>45390</v>
       </c>
@@ -11832,7 +11842,7 @@
         <v>0.239488602460776</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>45755</v>
       </c>
@@ -11861,7 +11871,7 @@
         <v>0.23808091327480499</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>45755</v>
       </c>
@@ -11890,7 +11900,7 @@
         <v>0.222510710112646</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>45390</v>
       </c>
@@ -11919,7 +11929,7 @@
         <v>0.20139055569469799</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>45454</v>
       </c>
@@ -11948,7 +11958,7 @@
         <v>0.19410472880238799</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>45390</v>
       </c>
@@ -11977,7 +11987,7 @@
         <v>0.178008568090116</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>45755</v>
       </c>
@@ -12006,7 +12016,7 @@
         <v>0.17778383010951301</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>45454</v>
       </c>
@@ -12035,7 +12045,7 @@
         <v>0.171237128282447</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>45755</v>
       </c>
@@ -12064,7 +12074,7 @@
         <v>0.13492133553001301</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>45755</v>
       </c>
@@ -12093,7 +12103,7 @@
         <v>0.134461116709475</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>45755</v>
       </c>
@@ -12122,7 +12132,7 @@
         <v>0.13194227667733399</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>45755</v>
       </c>
@@ -12151,7 +12161,7 @@
         <v>0.103692552629357</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>45755</v>
       </c>
@@ -12180,7 +12190,7 @@
         <v>9.6643633472066906E-2</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>45755</v>
       </c>
@@ -12209,7 +12219,7 @@
         <v>8.8144110230004694E-2</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>45454</v>
       </c>
@@ -12238,7 +12248,7 @@
         <v>8.7619824182035594E-2</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>45755</v>
       </c>
@@ -12267,7 +12277,7 @@
         <v>7.4846576989099606E-2</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>45755</v>
       </c>
@@ -12296,7 +12306,7 @@
         <v>7.3928012915403699E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>45755</v>
       </c>
@@ -12325,7 +12335,7 @@
         <v>7.3236587830780103E-2</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>45755</v>
       </c>
@@ -12354,7 +12364,7 @@
         <v>5.4223022180915501E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>45755</v>
       </c>
@@ -12383,7 +12393,7 @@
         <v>5.3253962806640999E-2</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>45755</v>
       </c>
@@ -12412,7 +12422,7 @@
         <v>4.9757930319564603E-2</v>
       </c>
     </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>45390</v>
       </c>
@@ -12441,7 +12451,7 @@
         <v>4.3378417744732403E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>45755</v>
       </c>
@@ -12470,7 +12480,7 @@
         <v>4.2188195929767601E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>45755</v>
       </c>
@@ -12499,7 +12509,7 @@
         <v>2.4989340369452901E-2</v>
       </c>
     </row>
-    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>45755</v>
       </c>
@@ -12528,7 +12538,7 @@
         <v>2.0491527857613899E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>45755</v>
       </c>
@@ -12557,7 +12567,7 @@
         <v>1.8967563767826601E-2</v>
       </c>
     </row>
-    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>45390</v>
       </c>
@@ -12586,7 +12596,7 @@
         <v>1.6393222286091101E-2</v>
       </c>
     </row>
-    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>45755</v>
       </c>
@@ -12615,7 +12625,7 @@
         <v>7.48332082949669E-3</v>
       </c>
     </row>
-    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>45390</v>
       </c>
@@ -12629,7 +12639,7 @@
         <v>1.6389981299999901</v>
       </c>
       <c r="E374" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F374">
         <v>27</v>
@@ -12644,7 +12654,7 @@
         <v>5.9866566635973497E-3</v>
       </c>
     </row>
-    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>45755</v>
       </c>
@@ -12673,7 +12683,7 @@
         <v>7.9137065981458004E-4</v>
       </c>
     </row>
-    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>45454</v>
       </c>
@@ -12702,7 +12712,7 @@
         <v>0.89795735450108605</v>
       </c>
     </row>
-    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>45454</v>
       </c>
@@ -12731,7 +12741,7 @@
         <v>0.893542105598922</v>
       </c>
     </row>
-    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>45454</v>
       </c>
@@ -12760,7 +12770,7 @@
         <v>0.49569590918898598</v>
       </c>
     </row>
-    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>45454</v>
       </c>
@@ -12789,7 +12799,7 @@
         <v>0.48344757261445098</v>
       </c>
     </row>
-    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <v>45454</v>
       </c>
@@ -12818,7 +12828,7 @@
         <v>0.41933072607598998</v>
       </c>
     </row>
-    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <v>45454</v>
       </c>
@@ -12847,7 +12857,7 @@
         <v>0.37204683629388502</v>
       </c>
     </row>
-    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>45454</v>
       </c>
@@ -12876,7 +12886,7 @@
         <v>0.369450234539552</v>
       </c>
     </row>
-    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>45454</v>
       </c>
@@ -12905,7 +12915,7 @@
         <v>0.34007732197658502</v>
       </c>
     </row>
-    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>45454</v>
       </c>
@@ -12934,7 +12944,7 @@
         <v>0.329884334709934</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>45454</v>
       </c>
@@ -12963,7 +12973,7 @@
         <v>0.29999599314872699</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <v>45454</v>
       </c>
@@ -12992,7 +13002,7 @@
         <v>0.29871872211280598</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
         <v>45454</v>
       </c>
@@ -13021,7 +13031,7 @@
         <v>0.23113398104260799</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <v>45454</v>
       </c>
@@ -13050,7 +13060,7 @@
         <v>0.13426201036190599</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <v>45454</v>
       </c>
@@ -13079,7 +13089,7 @@
         <v>0.119697212518976</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>45755</v>
       </c>
@@ -13108,7 +13118,7 @@
         <v>9.5804163222303396E-2</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <v>45454</v>
       </c>
@@ -13137,7 +13147,7 @@
         <v>6.2999340766808007E-2</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <v>45755</v>
       </c>
@@ -13166,7 +13176,7 @@
         <v>6.2153086147201303E-2</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <v>45755</v>
       </c>
@@ -13195,7 +13205,7 @@
         <v>5.8393673275935802E-2</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <v>45755</v>
       </c>
@@ -13224,7 +13234,7 @@
         <v>5.1045355361208501E-2</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
         <v>45755</v>
       </c>
@@ -13253,7 +13263,7 @@
         <v>4.7999723933700403E-2</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <v>45755</v>
       </c>
@@ -13282,7 +13292,7 @@
         <v>4.7428708488968602E-2</v>
       </c>
     </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
         <v>45454</v>
       </c>
@@ -13311,7 +13321,7 @@
         <v>4.1116317694414199E-2</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
         <v>45755</v>
       </c>
@@ -13340,7 +13350,7 @@
         <v>4.1031069218998899E-2</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
         <v>45755</v>
       </c>
@@ -13369,7 +13379,7 @@
         <v>3.9951529450746898E-2</v>
       </c>
     </row>
-    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <v>45755</v>
       </c>
@@ -13400,26 +13410,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J400" xr:uid="{10758E95-B21C-4274-9E23-53FE35BC8D40}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="23"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="8.2"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <filters>
-        <filter val="10m"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I400">
       <sortCondition ref="F1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
